--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96820</v>
+        <v>96823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96820</v>
+        <v>96823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27999-2025 artfynd.xlsx
+++ b/artfynd/A 27999-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>128964674</v>
       </c>
       <c r="B10" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128968892</v>
       </c>
       <c r="B11" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
